--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cristian.steopei/Downloads/CheckLists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cristian.steopei/Desktop/Learning/UBB-CS/ThirdYear/VVSS/MyDrinkShop/docs/Lab01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A58EDB-62C2-A747-97E5-D43B39655E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB547A6-4710-B143-9A0E-324AF98E4EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2360" yWindow="2060" windowWidth="29020" windowHeight="18100" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="120">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -640,6 +640,9 @@
   </si>
   <si>
     <t>Effort to perform tool-based code analysis (hours): 30min</t>
+  </si>
+  <si>
+    <t>Mora Dragos</t>
   </si>
 </sst>
 </file>
@@ -899,14 +902,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -926,25 +942,12 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1271,19 +1274,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1296,7 +1299,7 @@
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J3" s="17">
@@ -1307,14 +1310,14 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="22" t="s">
         <v>43</v>
       </c>
       <c r="J4" s="3">
@@ -1325,30 +1328,34 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="34"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="3">
+        <v>234</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="9" spans="1:10" ht="16">
       <c r="B9" s="10" t="s">
@@ -1589,19 +1596,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1614,7 +1621,7 @@
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J3" s="17">
@@ -1625,15 +1632,15 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="35"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="36" t="s">
-        <v>42</v>
+      <c r="I4" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="J4" s="3">
         <v>236</v>
@@ -1643,30 +1650,34 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="37"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="3">
+        <v>234</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -1910,19 +1921,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1935,7 +1946,7 @@
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="22" t="s">
         <v>59</v>
       </c>
       <c r="J3" s="17">
@@ -1946,14 +1957,14 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="30"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="22" t="s">
         <v>43</v>
       </c>
       <c r="J4" s="3">
@@ -1964,30 +1975,34 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="33"/>
+      <c r="D5" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="39"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="3">
+        <v>234</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
     </row>
     <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
@@ -2262,7 +2277,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="12"/>
-      <c r="E32" s="37" t="s">
+      <c r="E32" s="23" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2304,19 +2319,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -2329,7 +2344,7 @@
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="22" t="s">
         <v>42</v>
       </c>
       <c r="J3" s="17">
@@ -2340,14 +2355,14 @@
       <c r="C4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="30"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="22" t="s">
         <v>43</v>
       </c>
       <c r="J4" s="3">
@@ -2358,12 +2373,14 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="22" t="s">
+        <v>119</v>
+      </c>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10">
@@ -2371,8 +2388,8 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10">
@@ -2402,10 +2419,10 @@
       <c r="D10" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="24" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2416,10 +2433,10 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="25" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2430,10 +2447,10 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="25" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2448,10 +2465,10 @@
       <c r="D13" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="24" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2466,10 +2483,10 @@
       <c r="D14" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="24" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2479,9 +2496,9 @@
         <v>6</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="39" t="s">
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="25" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2492,8 +2509,8 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39" t="s">
+      <c r="E16" s="25"/>
+      <c r="F16" s="25" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2505,10 +2522,10 @@
       <c r="C17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="24" t="s">
         <v>109</v>
       </c>
       <c r="F17" s="2"/>
@@ -2524,10 +2541,10 @@
       <c r="D18" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="25" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2652,11 +2669,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="34" t="s">
+      <c r="C32" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
       <c r="F32" s="18"/>
     </row>
     <row r="35" spans="6:6">
